--- a/www/download/IND.hours_worked.empe_hs.r.pc.rpO1.xlsx
+++ b/www/download/IND.hours_worked.empe_hs.r.pc.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>0.10955143095146</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>0.114780512886299</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>0.120147617578139</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>0.12567559535655</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>0.131389805509691</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>0.137318730790312</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>0.143494728361388</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>0.148230307978723</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>0.151492247330357</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>0.148429770757862</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>0.146205954496901</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>0.146205954496901</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>0.146205954496901</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>0.146205954496901</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>0.146205954496901</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>0.113137247731648</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>0.1130773975395</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113718272828169</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>0.11418334035063</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.136361356854577</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>0.139704039706494</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>0.140254486022889</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>0.144158214523391</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>0.143225011137814</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>0.174623171220739</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>0.168877336334161</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0.164995263524689</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>0.167797619169898</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>0.163870769885039</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>0.175496739843436</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>0.115659741544566</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>0.119230744064524</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>0.122177648215674</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>0.124250611989703</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>0.125694294726123</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>0.127273408489188</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>0.129670759247346</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>0.13126738276117</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>0.132653441270207</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>0.139381275156615</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.141954420237789</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>0.142477529378672</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>0.148554207443421</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>0.170539732797016</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>0.172267612866357</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785096043442988</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>0.0783260088229312</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.0725635829408859</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0671800623138325</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.0688251783923756</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>0.0699078324120806</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0692388796418979</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0.0724385050920685</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>0.0880048178129122</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.0921735966508009</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0974095903387319</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>0.101508629331494</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>0.105364824723641</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115065358467651</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>0.120196730948339</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>0.110215680880114</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>0.112243117090419</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>0.114270553300723</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>0.116297989511028</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>0.118325425721333</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>0.120352861931638</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>0.122380298141942</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>0.124407734352247</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>0.127782000052277</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>0.131156265752308</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>0.134530531452338</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.142041661732327</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>0.149552792012316</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>0.157063922292304</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>0.164575052572293</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>0.144678943718754</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>0.145974864030428</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>0.149052670820783</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>0.153333749670552</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.152771261677904</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>0.15853507878715</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>0.16454051150029</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>0.16732354439901</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>0.170852123624246</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>0.173805592370665</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>0.181409266638102</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>0.189414445328348</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>0.197587086459988</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>0.195460971524824</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.205496764228743</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>0.0463005508328902</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>0.0487470639722212</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>0.0512995826534342</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0539610480363788</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>0.056734370862934</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>0.0596224229662163</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>0.0626280285504751</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.0657539552756941</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.072556037345357</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>0.0755835939356043</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>0.0867325066632651</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.097428836119497</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>0.0941310138522617</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.100846173037866</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0.100846173037866</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>0.29501632942481</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>0.293308740062344</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>0.280608690472955</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>0.267314716451038</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>0.267813512574648</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>0.271519071909591</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>0.271893085468395</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>0.278524698977206</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.280286225135778</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.279550377287939</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>0.265568736297898</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>0.274163910756846</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>0.293637463282541</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>0.302300726860568</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>0.302163821283627</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>0.10022616651815</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>0.10022616651815</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>0.10022616651815</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>0.10022616651815</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>0.102469307678463</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>0.1048336444026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>0.107287624360311</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.11085272498633</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>0.111754106723243</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>0.118224859000065</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>0.120142272903144</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>0.123403193107016</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>0.123442430242449</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>0.130484887563702</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>0.14159480219758</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>0.195115628492194</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>0.195838904275002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>0.196825263313754</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>0.208303944300909</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>0.20555775804634</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>0.204559713203882</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>0.208305012463317</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>0.213422469992099</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>0.227905040231277</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.233830997800985</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>0.22946619900437</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>0.22343403545077</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>0.220789162547975</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>0.227133454897749</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0.24001300599493</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>0.184484225292462</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.191150044073375</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>0.197675761217595</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>0.204353656310667</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.208209712703704</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>0.209484889795474</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>0.216057403459574</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>0.223162201987542</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0.249969179148038</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>0.252773922421227</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>0.265380467619703</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>0.268520250599075</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.240725825229757</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>0.264590109238242</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>0.266483772258316</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>0.200670069665548</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>0.218043292182423</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>0.224069172303285</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>0.239637678914906</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>0.247476783015023</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>0.266639805201482</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>0.275602465726367</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>0.282187873220182</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>0.289157307595638</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>0.297779523753416</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>0.310856327494752</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>31.67</t>
+          <t>0.316681289933401</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>0.3208652051446</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>0.32467331842563</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>0.336291443854847</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>0.312193990390098</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>0.307799396730762</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>0.297775294325577</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>0.28689935380008</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>0.279698251361371</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>0.283787914224018</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.285719455533138</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>0.292066846754811</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>0.28539735666268</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>0.299631050602165</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>0.317499404467549</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>0.313093618797607</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>0.313726742537568</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>0.317492685976851</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>0.330632029949086</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>0.273962792452623</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>0.280187048772489</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>0.283290645672041</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>0.282732007640922</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>0.285006629270886</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>0.285377458913775</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>0.288824914960104</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>0.292661282276355</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>0.297260406877777</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>0.303567149908334</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0.304474725809539</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>0.307989294577137</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>0.316946499155567</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>0.320349632916784</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>0.337259191383188</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>0.178882226288668</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>0.185597921936273</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>0.192858300507947</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199570790221848</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>0.208919542052195</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213566804948409</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>0.219675442988159</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>0.223994541614104</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>0.226462628785401</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>0.233923943837903</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>0.246721743340155</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>0.257805244546523</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>0.263564455118843</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>0.271010633571281</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>0.288307021141222</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>0.189766274996681</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>0.190379047097163</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>0.203799425594425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>0.216388318268939</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>0.230560399126563</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>0.243414760669638</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>0.248715498768196</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>0.258058419418581</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>0.259437706930295</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>0.255510329270998</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>0.259812932362462</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>0.269235322839665</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>0.28630327573404</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>0.28719214049374</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>0.290226513831573</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>0.172193539866581</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>0.17704560351668</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>0.179749176991545</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>0.182463532496045</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175757547097627</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>0.180077572106593</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>0.178048293074848</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.185226550922153</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>0.188413467972605</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>0.200397403569388</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>0.199401207613155</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.210451308834914</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>0.216063946478499</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>0.220359943781744</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>0.22116539207647</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>0.130850879536823</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>0.130850879536823</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>0.130850879536823</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>0.130850879536823</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>0.144064009987499</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.136418385920244</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>0.137101331933868</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>0.138390127093662</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>0.145542680314531</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>0.160630703934852</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>0.165916046885304</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0.16998333704836</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>0.170997793877179</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>0.184809619463623</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>0.18737099784991</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>0.0566899406941814</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>0.0643997535174709</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>0.0620781901604071</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>0.0703749051182925</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>0.0715979891524097</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>0.0829424277174645</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>0.082612516283083</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0.0841527025971551</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>0.0782006947582791</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>0.0866247519904517</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>0.0927822374252588</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>0.0989397228600659</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>0.0927684627595972</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>0.0927684627595972</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>0.0927684627595972</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.136395434894175</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>0.138168353847534</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>0.139941272800893</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>0.141714191754252</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>0.143487110707611</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15.31</t>
+          <t>0.153075098503735</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>0.162663086299858</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>0.172251074095982</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.181839061892105</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191427049688229</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191427049688229</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191427049688229</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191427049688229</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191427049688229</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191427049688229</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>0.189554344070667</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>0.201418712090427</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>0.205601942560401</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>0.2151627525334</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>0.224272432322089</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.228917850140343</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>0.234596609399241</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>0.251870921354052</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>0.268609409539807</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.287257104030716</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>0.294773786798651</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.310305463091801</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>0.323984639496917</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.338950725981488</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>0.366725580736755</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>0.0717110126405763</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>0.0753669150529157</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>0.0793565771445653</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0832941413248145</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>0.0899404408524558</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>0.0910168375199489</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>0.0937301852919814</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>0.0974894162572822</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>0.102150559963198</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>0.0971776740057303</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>0.108058588631121</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>0.115701311228379</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>0.121575422221856</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>0.135136273934228</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>0.131157776772808</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>0.176103671050398</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>0.181697703233158</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>0.186458713053473</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>0.194808241514536</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>0.201402010307351</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>0.205911665137453</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>0.214744745649853</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>0.223659019567716</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>0.227076064331132</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>0.229607364074536</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230215857060902</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230215857060902</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230215857060902</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230215857060902</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230215857060902</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>0.264457196852025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>0.279162503358605</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>0.289349291432411</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>0.313902096132527</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>0.325542157096532</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>32.71</t>
+          <t>0.32708265847282</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>0.342450577055497</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>0.372650802730414</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>0.379068724074233</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>0.385820132625152</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398516741084111</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398516741084111</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398516741084111</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398516741084111</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398516741084111</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>0.266277538684155</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26.21</t>
+          <t>0.262117929860927</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>0.253299215853023</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>0.244044451439439</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>0.23726177005492</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.239032304805718</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>0.239857012683979</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>0.246429012006655</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>0.263919508581308</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>0.26640937752232</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>0.278650240628368</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>0.283375972739592</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>0.297986422791148</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>0.304431719963992</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>0.317696418422825</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>0.187988986031401</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>0.174369102208575</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>0.170358249670412</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.166459898907562</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>0.162894742779448</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>0.162231261084635</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.161585271617819</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162442826252358</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>0.117287519285537</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>0.204285184323656</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>0.219649700320424</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.193609835066314</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>0.212430474142803</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>0.207397959744257</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>0.269903493699397</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>0.221402598356645</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>0.217783825319958</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>0.20956731176511</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>0.201145532179456</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>0.196767345891568</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>0.19894241748371</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>0.19874063203842</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>0.204052674995567</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>0.187227688565911</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>0.211098684816096</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197425017902899</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>0.201618232029366</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>0.218079798267664</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.24652483085632</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>0.24740962224875</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.166978214733434</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>0.164273785807949</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162350250898461</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.163072638911295</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162399093243958</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>0.163773526307836</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>0.163949268337681</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.163292241697544</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>0.163358998863344</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.16308706374245</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>0.162973214075747</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0.159299880923452</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0.159299880923452</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0.159299880923452</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0.159299880923452</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785096043442988</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>0.0783260088229312</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.0725635829408859</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0671800623138325</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.0688251783923756</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>0.0699078324120806</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0692388796418979</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0.0724385050920685</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>0.0880048178129122</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.0921735966508009</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0974095903387319</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>0.101508629331494</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>0.105364824723641</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115065358467651</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>0.120196730948339</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>0.155191376679913</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>0.165497267868503</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>0.185297732881203</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>0.181065654202141</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>0.207357069565396</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>0.190483692599167</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>0.182531352602225</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.200458681164414</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>0.226943761394089</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>0.245957121096906</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>0.251300472282877</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>0.250128342330687</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.248987793745188</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>0.258089129993417</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>0.264563599615033</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043564712389</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043564712389</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043564712389</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043564712389</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043564712389</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043564712389</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.133271213275365</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>0.141719800156731</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>0.156956740225659</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>0.17755604537419</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>0.188549726720077</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>0.196122066802558</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.201049411020539</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>0.203680734714193</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>0.220249348393439</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785096043442988</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>0.0783260088229312</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.0725635829408859</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0671800623138325</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.0688251783923756</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>0.0699078324120806</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0692388796418979</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0.0724385050920685</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>0.0880048178129122</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.0921735966508009</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0974095903387319</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>0.101508629331494</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>0.105364824723641</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115065358467651</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>0.120196730948339</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785096043442988</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>0.0783260088229312</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.0725635829408859</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0671800623138325</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.0688251783923756</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>0.0699078324120806</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0692388796418979</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0.0724385050920685</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>0.0880048178129122</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.0921735966508009</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0974095903387319</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>0.101508629331494</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>0.105364824723641</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115065358467651</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>0.120196730948339</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952203931999555</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952203931999555</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952203931999555</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952203931999555</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>0.0974996594531083</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>0.0998463999092194</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>0.102225782181053</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>0.105809265803734</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>0.108864527433162</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>0.111259696098933</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113630104897906</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113630104897906</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113630104897906</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113630104897906</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113630104897906</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>0.10880632060207</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>0.10880632060207</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>0.10880632060207</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>0.10880632060207</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>0.102932231374819</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>0.103885773438721</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>0.107318689593067</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>0.109055839789039</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115067432691534</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>0.121046962340549</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>0.1335667069695</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>0.139539346363986</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>0.137991242044482</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>0.138555441233436</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>0.146646103261557</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>0.146828127940186</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>0.146828127940186</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>0.146828127940186</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>0.146828127940186</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>0.153428418671205</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>0.163047805157799</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>0.134658971574206</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>0.148873839431078</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>0.169459064090797</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>0.179940913358341</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>0.186909815187493</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.198040398164625</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>0.202323456638045</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>0.209431689172736</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>0.223685859238385</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>0.127366819728121</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>0.129160847897513</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>0.133416182165984</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>0.137055627698075</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>0.1464484811306</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>0.164891415642487</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>0.172730142899479</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>0.176779161263421</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>0.179782694531231</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>0.187163260028709</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>0.198873353722608</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>0.210336155623757</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>0.215609489132964</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>0.230321399524585</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>0.240881984702742</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>0.0981629125401097</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>0.103058831998176</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>0.116034672772349</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>0.109895843177414</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>0.118474430887221</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>0.12379939560193</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>0.129729007768924</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>0.135899362035964</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>0.145703638911846</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>0.134170871828341</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141029324945294</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>0.147403173888492</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>0.153634078765284</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>0.157996225929737</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162358373094191</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>0.214223984649701</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>0.221762082415447</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>0.229300180181193</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>0.236838277946938</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>0.244376375712684</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>0.25191447347843</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>0.259452571244176</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>0.266990669009922</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>0.274297445852658</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>0.281604222695395</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>0.289922249231759</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>0.308288891565255</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>0.304642425381812</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317551555991869</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.341667640070491</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>0.218959302225379</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>0.219126429312119</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>0.220748431530531</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>0.226290023236293</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>0.227049318701311</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>0.229904784708502</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>0.234548729053835</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>0.235991254564596</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>0.23231094231555</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>0.244305192036868</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>0.24660362088919</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>0.250359099446739</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>0.251805968717819</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>0.255890685345024</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>0.26432732549474</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.155282646906169</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>0.157701180745512</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>0.159117651873489</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>0.160829657779038</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>0.164682133111337</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>0.168121531150933</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.170713780599449</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>0.176732786541879</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>0.182257267892264</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>0.191332324721546</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>0.196486156235948</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.200505416481349</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>0.204207737261477</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>0.210861564497349</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>0.219257860870625</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.155282646906169</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>0.157701180745512</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>0.159117651873489</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>0.160829657779038</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>0.164682133111337</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>0.168121531150933</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.170713780599449</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>0.176732786541879</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>0.182257267892264</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>0.191332324721546</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>0.196486156235948</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.200505416481349</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>0.204207737261477</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>0.210861564497349</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>0.219257860870625</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
